--- a/data/property/checked/NOV2025_codedAndCategorised.xlsx
+++ b/data/property/checked/NOV2025_codedAndCategorised.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Mat\property\data\property\checked\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E84468F3-04B0-47D0-A450-DA54FCAE8EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E439408-F70C-447A-92D3-BAC95F33BD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{09F7DB9E-57D0-4BEE-A79F-4FF06485563A}"/>
+    <workbookView xWindow="28830" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{09F7DB9E-57D0-4BEE-A79F-4FF06485563A}"/>
   </bookViews>
   <sheets>
     <sheet name="NOV2025_codedAndCategorised" sheetId="1" r:id="rId1"/>
@@ -1986,6 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B6550E-C6E8-4640-92B4-9AD60B0000E3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I319"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2029,7 +2030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45962</v>
       </c>
@@ -2049,7 +2050,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45962</v>
       </c>
@@ -2069,7 +2070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45962</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45962</v>
       </c>
@@ -2112,7 +2113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45962</v>
       </c>
@@ -2135,7 +2136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45962</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45962</v>
       </c>
@@ -2181,7 +2182,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45962</v>
       </c>
@@ -2201,7 +2202,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45962</v>
       </c>
@@ -2224,7 +2225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45962</v>
       </c>
@@ -2247,7 +2248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45963</v>
       </c>
@@ -2270,7 +2271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45963</v>
       </c>
@@ -2667,7 +2668,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45964</v>
       </c>
@@ -2710,7 +2711,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45964</v>
       </c>
@@ -2733,7 +2734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45964</v>
       </c>
@@ -2754,7 +2755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45964</v>
       </c>
@@ -2775,7 +2776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45964</v>
       </c>
@@ -2798,7 +2799,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45964</v>
       </c>
@@ -2818,7 +2819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45964</v>
       </c>
@@ -2864,7 +2865,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45964</v>
       </c>
@@ -2887,7 +2888,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45964</v>
       </c>
@@ -2910,7 +2911,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45964</v>
       </c>
@@ -2956,7 +2957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45964</v>
       </c>
@@ -2976,7 +2977,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45964</v>
       </c>
@@ -3019,7 +3020,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45964</v>
       </c>
@@ -3065,7 +3066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45964</v>
       </c>
@@ -3085,7 +3086,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45964</v>
       </c>
@@ -3105,7 +3106,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45964</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45964</v>
       </c>
@@ -3148,7 +3149,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45964</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45964</v>
       </c>
@@ -3191,7 +3192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45964</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45964</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45964</v>
       </c>
@@ -3251,7 +3252,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45964</v>
       </c>
@@ -3271,7 +3272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45964</v>
       </c>
@@ -3294,7 +3295,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45964</v>
       </c>
@@ -3314,7 +3315,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45965</v>
       </c>
@@ -3337,7 +3338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45965</v>
       </c>
@@ -3360,7 +3361,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45965</v>
       </c>
@@ -3380,7 +3381,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45965</v>
       </c>
@@ -3403,7 +3404,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45965</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45965</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45965</v>
       </c>
@@ -3466,7 +3467,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45965</v>
       </c>
@@ -3489,7 +3490,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45965</v>
       </c>
@@ -3512,7 +3513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45965</v>
       </c>
@@ -3535,7 +3536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45966</v>
       </c>
@@ -3555,7 +3556,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45966</v>
       </c>
@@ -3601,7 +3602,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45966</v>
       </c>
@@ -3624,7 +3625,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45966</v>
       </c>
@@ -3647,7 +3648,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45966</v>
       </c>
@@ -3670,7 +3671,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45966</v>
       </c>
@@ -3693,7 +3694,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45967</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45967</v>
       </c>
@@ -3736,7 +3737,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45967</v>
       </c>
@@ -3759,7 +3760,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45967</v>
       </c>
@@ -3782,7 +3783,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45967</v>
       </c>
@@ -3805,7 +3806,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45967</v>
       </c>
@@ -3828,7 +3829,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45967</v>
       </c>
@@ -3851,7 +3852,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45967</v>
       </c>
@@ -3874,7 +3875,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45967</v>
       </c>
@@ -3897,7 +3898,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45967</v>
       </c>
@@ -3920,7 +3921,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45967</v>
       </c>
@@ -3940,7 +3941,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45968</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45968</v>
       </c>
@@ -3986,7 +3987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45968</v>
       </c>
@@ -4006,7 +4007,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45968</v>
       </c>
@@ -4029,7 +4030,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45968</v>
       </c>
@@ -4052,7 +4053,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45968</v>
       </c>
@@ -4075,7 +4076,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45968</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45968</v>
       </c>
@@ -4121,7 +4122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>45968</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>45968</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>45968</v>
       </c>
@@ -4187,7 +4188,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>45968</v>
       </c>
@@ -4210,7 +4211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>45969</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>45969</v>
       </c>
@@ -4256,7 +4257,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>45970</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>45970</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>45970</v>
       </c>
@@ -4323,7 +4324,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>45970</v>
       </c>
@@ -4346,7 +4347,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>45971</v>
       </c>
@@ -4369,7 +4370,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>45971</v>
       </c>
@@ -4392,7 +4393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>45971</v>
       </c>
@@ -4415,7 +4416,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>45971</v>
       </c>
@@ -4438,7 +4439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>45971</v>
       </c>
@@ -4461,7 +4462,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>45971</v>
       </c>
@@ -4484,7 +4485,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>45971</v>
       </c>
@@ -4507,7 +4508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>45971</v>
       </c>
@@ -4530,7 +4531,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>45971</v>
       </c>
@@ -4553,7 +4554,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>45971</v>
       </c>
@@ -4622,7 +4623,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>45971</v>
       </c>
@@ -4668,7 +4669,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>45972</v>
       </c>
@@ -4691,7 +4692,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>45972</v>
       </c>
@@ -4714,7 +4715,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>45972</v>
       </c>
@@ -4735,7 +4736,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>45972</v>
       </c>
@@ -4758,7 +4759,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>45972</v>
       </c>
@@ -4781,7 +4782,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>45972</v>
       </c>
@@ -4804,7 +4805,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>45972</v>
       </c>
@@ -4827,7 +4828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>45972</v>
       </c>
@@ -4850,7 +4851,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>45972</v>
       </c>
@@ -4870,7 +4871,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>45972</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>45972</v>
       </c>
@@ -4916,7 +4917,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>45972</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>45973</v>
       </c>
@@ -4982,7 +4983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>45973</v>
       </c>
@@ -5005,7 +5006,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>45973</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>45973</v>
       </c>
@@ -5048,7 +5049,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>45973</v>
       </c>
@@ -5071,7 +5072,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>45973</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>45973</v>
       </c>
@@ -5117,7 +5118,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>45973</v>
       </c>
@@ -5140,7 +5141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>45974</v>
       </c>
@@ -5163,7 +5164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>45974</v>
       </c>
@@ -5186,7 +5187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>45974</v>
       </c>
@@ -5209,7 +5210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>45974</v>
       </c>
@@ -5232,7 +5233,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>45974</v>
       </c>
@@ -5255,7 +5256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>45974</v>
       </c>
@@ -5278,7 +5279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>45974</v>
       </c>
@@ -5301,7 +5302,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>45974</v>
       </c>
@@ -5324,7 +5325,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>45974</v>
       </c>
@@ -5345,7 +5346,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>45974</v>
       </c>
@@ -5368,7 +5369,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>45975</v>
       </c>
@@ -5388,7 +5389,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>45975</v>
       </c>
@@ -5411,7 +5412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>45975</v>
       </c>
@@ -5434,7 +5435,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>45975</v>
       </c>
@@ -5457,7 +5458,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>45975</v>
       </c>
@@ -5480,7 +5481,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>45975</v>
       </c>
@@ -5503,7 +5504,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>45975</v>
       </c>
@@ -5526,7 +5527,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>45975</v>
       </c>
@@ -5549,7 +5550,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>45976</v>
       </c>
@@ -5572,7 +5573,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>45976</v>
       </c>
@@ -5595,7 +5596,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>45976</v>
       </c>
@@ -5618,7 +5619,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>45977</v>
       </c>
@@ -5641,7 +5642,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>45977</v>
       </c>
@@ -5664,7 +5665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>45977</v>
       </c>
@@ -5687,7 +5688,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>45977</v>
       </c>
@@ -5710,7 +5711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>45977</v>
       </c>
@@ -5733,7 +5734,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>45977</v>
       </c>
@@ -5756,7 +5757,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>45978</v>
       </c>
@@ -5779,7 +5780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>45978</v>
       </c>
@@ -5802,7 +5803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>45978</v>
       </c>
@@ -5825,7 +5826,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>45978</v>
       </c>
@@ -5848,7 +5849,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>45978</v>
       </c>
@@ -5914,7 +5915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>45978</v>
       </c>
@@ -5980,7 +5981,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>45978</v>
       </c>
@@ -6003,7 +6004,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>45978</v>
       </c>
@@ -6072,7 +6073,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>45978</v>
       </c>
@@ -6144,7 +6145,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>45978</v>
       </c>
@@ -6260,7 +6261,7 @@
       </c>
       <c r="I189" s="5"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>45978</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>45979</v>
       </c>
@@ -6304,7 +6305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>45979</v>
       </c>
@@ -6327,7 +6328,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>45979</v>
       </c>
@@ -6347,7 +6348,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>45979</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>45979</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>45979</v>
       </c>
@@ -6414,7 +6415,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>45979</v>
       </c>
@@ -6435,7 +6436,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>45979</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>45979</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>45979</v>
       </c>
@@ -6527,7 +6528,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>45980</v>
       </c>
@@ -6547,7 +6548,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>45980</v>
       </c>
@@ -6570,7 +6571,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>45980</v>
       </c>
@@ -6593,7 +6594,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>45980</v>
       </c>
@@ -6616,7 +6617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>45980</v>
       </c>
@@ -6639,7 +6640,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>45981</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>45981</v>
       </c>
@@ -6685,7 +6686,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>45981</v>
       </c>
@@ -6708,7 +6709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>45981</v>
       </c>
@@ -6728,7 +6729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>45981</v>
       </c>
@@ -6751,7 +6752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>45981</v>
       </c>
@@ -6774,7 +6775,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>45981</v>
       </c>
@@ -6797,7 +6798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>45981</v>
       </c>
@@ -6817,7 +6818,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>45981</v>
       </c>
@@ -6840,7 +6841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>45981</v>
       </c>
@@ -6863,7 +6864,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>45981</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>45982</v>
       </c>
@@ -6906,7 +6907,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>45982</v>
       </c>
@@ -6929,7 +6930,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>45982</v>
       </c>
@@ -6952,7 +6953,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>45982</v>
       </c>
@@ -6975,7 +6976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>45982</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>45982</v>
       </c>
@@ -7021,7 +7022,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>45982</v>
       </c>
@@ -7044,7 +7045,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>45983</v>
       </c>
@@ -7067,7 +7068,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>45983</v>
       </c>
@@ -7090,7 +7091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>45984</v>
       </c>
@@ -7113,7 +7114,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>45984</v>
       </c>
@@ -7136,7 +7137,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>45984</v>
       </c>
@@ -7159,7 +7160,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>45985</v>
       </c>
@@ -7179,7 +7180,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>45985</v>
       </c>
@@ -7202,7 +7203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>45985</v>
       </c>
@@ -7225,7 +7226,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>45985</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>45985</v>
       </c>
@@ -7271,7 +7272,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>45985</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>45985</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>45985</v>
       </c>
@@ -7363,7 +7364,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>45985</v>
       </c>
@@ -7386,7 +7387,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>45985</v>
       </c>
@@ -7406,7 +7407,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>45985</v>
       </c>
@@ -7429,7 +7430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>45985</v>
       </c>
@@ -7452,7 +7453,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>45985</v>
       </c>
@@ -7475,7 +7476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>45985</v>
       </c>
@@ -7498,7 +7499,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>45985</v>
       </c>
@@ -7521,7 +7522,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>45985</v>
       </c>
@@ -7544,7 +7545,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>45985</v>
       </c>
@@ -7567,7 +7568,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>45985</v>
       </c>
@@ -7587,7 +7588,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>45985</v>
       </c>
@@ -7610,7 +7611,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>45985</v>
       </c>
@@ -7630,7 +7631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>45986</v>
       </c>
@@ -7653,7 +7654,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>45986</v>
       </c>
@@ -7676,7 +7677,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>45986</v>
       </c>
@@ -7699,7 +7700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>45986</v>
       </c>
@@ -7722,7 +7723,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>45986</v>
       </c>
@@ -7745,7 +7746,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>45986</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>45986</v>
       </c>
@@ -7788,7 +7789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>45986</v>
       </c>
@@ -7811,7 +7812,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>45986</v>
       </c>
@@ -7834,7 +7835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>45986</v>
       </c>
@@ -7857,7 +7858,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>45986</v>
       </c>
@@ -7880,7 +7881,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>45986</v>
       </c>
@@ -7903,7 +7904,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>45987</v>
       </c>
@@ -7923,7 +7924,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>45987</v>
       </c>
@@ -7946,7 +7947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>45987</v>
       </c>
@@ -7969,7 +7970,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>45987</v>
       </c>
@@ -7992,7 +7993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>45987</v>
       </c>
@@ -8013,7 +8014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>45987</v>
       </c>
@@ -8036,7 +8037,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>45987</v>
       </c>
@@ -8059,7 +8060,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>45987</v>
       </c>
@@ -8082,7 +8083,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>45987</v>
       </c>
@@ -8105,7 +8106,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>45987</v>
       </c>
@@ -8128,7 +8129,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>45987</v>
       </c>
@@ -8148,7 +8149,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>45987</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>45987</v>
       </c>
@@ -8191,7 +8192,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>45987</v>
       </c>
@@ -8211,7 +8212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>45987</v>
       </c>
@@ -8234,7 +8235,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>45988</v>
       </c>
@@ -8257,7 +8258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>45988</v>
       </c>
@@ -8280,7 +8281,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>45988</v>
       </c>
@@ -8303,7 +8304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>45988</v>
       </c>
@@ -8326,7 +8327,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>45988</v>
       </c>
@@ -8349,7 +8350,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>45988</v>
       </c>
@@ -8369,7 +8370,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>45988</v>
       </c>
@@ -8392,7 +8393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>45988</v>
       </c>
@@ -8415,7 +8416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>45988</v>
       </c>
@@ -8435,7 +8436,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>45988</v>
       </c>
@@ -8458,7 +8459,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>45988</v>
       </c>
@@ -8481,7 +8482,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>45988</v>
       </c>
@@ -8504,7 +8505,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>45988</v>
       </c>
@@ -8527,7 +8528,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>45988</v>
       </c>
@@ -8547,7 +8548,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>45988</v>
       </c>
@@ -8570,7 +8571,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>45988</v>
       </c>
@@ -8593,7 +8594,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>45989</v>
       </c>
@@ -8613,7 +8614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>45989</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>45989</v>
       </c>
@@ -8659,7 +8660,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>45989</v>
       </c>
@@ -8682,7 +8683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>45989</v>
       </c>
@@ -8705,7 +8706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>45989</v>
       </c>
@@ -8774,7 +8775,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>45989</v>
       </c>
@@ -8820,7 +8821,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>45989</v>
       </c>
@@ -8843,7 +8844,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>45989</v>
       </c>
@@ -8866,7 +8867,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>45989</v>
       </c>
@@ -8886,7 +8887,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>45989</v>
       </c>
@@ -8909,7 +8910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>45989</v>
       </c>
@@ -8932,7 +8933,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>45989</v>
       </c>
@@ -8978,7 +8979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>45990</v>
       </c>
@@ -9001,7 +9002,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>45990</v>
       </c>
@@ -9024,7 +9025,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>45990</v>
       </c>
@@ -9047,7 +9048,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>45990</v>
       </c>
@@ -9070,7 +9071,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>45990</v>
       </c>
@@ -9093,7 +9094,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>45991</v>
       </c>
@@ -9113,7 +9114,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>45991</v>
       </c>
@@ -9136,7 +9137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>45991</v>
       </c>
@@ -9159,7 +9160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>45991</v>
       </c>
@@ -9180,7 +9181,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I319" xr:uid="{19B6550E-C6E8-4640-92B4-9AD60B0000E3}"/>
+  <autoFilter ref="A1:I319" xr:uid="{19B6550E-C6E8-4640-92B4-9AD60B0000E3}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Mortgage"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>